--- a/backend/src/main/resources/initial-data/assets_plan_20260629.xlsx
+++ b/backend/src/main/resources/initial-data/assets_plan_20260629.xlsx
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="F13">
-        <v>3204000</v>
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="I13">
-        <v>3204000</v>
+        <v>0</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="F14">
-        <v>768300</v>
+        <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="I14">
-        <v>768300</v>
+        <v>0</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="F15">
-        <v>494970</v>
+        <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="I15">
-        <v>494970</v>
+        <v>0</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F16">
-        <v>365560</v>
+        <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="I16">
-        <v>365560</v>
+        <v>0</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="F17">
-        <v>70140</v>
+        <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="I17">
-        <v>70140</v>
+        <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="F18">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         </is>
       </c>
       <c r="I18">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>

--- a/backend/src/main/resources/initial-data/assets_plan_20260629.xlsx
+++ b/backend/src/main/resources/initial-data/assets_plan_20260629.xlsx
@@ -57,6 +57,12 @@
           <t>명의</t>
         </is>
       </c>
+      <c r="K1">
+        <v>확정일</v>
+      </c>
+      <c r="L1">
+        <v>결제일</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -92,11 +98,6 @@
           <t>부채</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="I2">
         <v>239200000</v>
       </c>
@@ -140,11 +141,6 @@
           <t>자산</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="I3">
         <v>6639038</v>
       </c>
@@ -188,11 +184,6 @@
           <t>자산</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="I4">
         <v>5010000</v>
       </c>
@@ -236,11 +227,6 @@
           <t>자산</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="I5">
         <v>74176</v>
       </c>
@@ -284,11 +270,6 @@
           <t>자산</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="I6">
         <v>398</v>
       </c>
@@ -332,11 +313,6 @@
           <t>자산</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="I7">
         <v>0</v>
       </c>
@@ -380,11 +356,6 @@
           <t>자산</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="I8">
         <v>0</v>
       </c>
@@ -428,11 +399,6 @@
           <t>자산</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="I9">
         <v>210244</v>
       </c>
@@ -476,11 +442,6 @@
           <t>자산</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="I10">
         <v>64876</v>
       </c>
@@ -524,11 +485,6 @@
           <t>자산</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="I11">
         <v>26</v>
       </c>
@@ -572,11 +528,6 @@
           <t>자산</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="I12">
         <v>2</v>
       </c>
@@ -620,11 +571,6 @@
           <t>부채</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="I13">
         <v>0</v>
       </c>
@@ -632,6 +578,12 @@
         <is>
           <t>석수</t>
         </is>
+      </c>
+      <c r="K13">
+        <v>16</v>
+      </c>
+      <c r="L13">
+        <v>25</v>
       </c>
     </row>
     <row r="14">
@@ -668,11 +620,6 @@
           <t>부채</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="I14">
         <v>0</v>
       </c>
@@ -680,6 +627,12 @@
         <is>
           <t>석수</t>
         </is>
+      </c>
+      <c r="K14">
+        <v>16</v>
+      </c>
+      <c r="L14">
+        <v>25</v>
       </c>
     </row>
     <row r="15">
@@ -716,11 +669,6 @@
           <t>부채</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="I15">
         <v>0</v>
       </c>
@@ -728,6 +676,12 @@
         <is>
           <t>석수</t>
         </is>
+      </c>
+      <c r="K15">
+        <v>16</v>
+      </c>
+      <c r="L15">
+        <v>25</v>
       </c>
     </row>
     <row r="16">
@@ -764,11 +718,6 @@
           <t>부채</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="I16">
         <v>0</v>
       </c>
@@ -776,6 +725,12 @@
         <is>
           <t>석수</t>
         </is>
+      </c>
+      <c r="K16">
+        <v>16</v>
+      </c>
+      <c r="L16">
+        <v>25</v>
       </c>
     </row>
     <row r="17">
@@ -812,11 +767,6 @@
           <t>부채</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="I17">
         <v>0</v>
       </c>
@@ -824,6 +774,12 @@
         <is>
           <t>석수</t>
         </is>
+      </c>
+      <c r="K17">
+        <v>16</v>
+      </c>
+      <c r="L17">
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -860,11 +816,6 @@
           <t>부채</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="I18">
         <v>0</v>
       </c>
@@ -872,6 +823,12 @@
         <is>
           <t>석수</t>
         </is>
+      </c>
+      <c r="K18">
+        <v>16</v>
+      </c>
+      <c r="L18">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
